--- a/output/laminas_comunales/comunal_i_peringrmin_a_2024_atacama.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2024_atacama.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -405,9 +400,6 @@
       <c r="E2">
         <v>10.51587301587302</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -427,9 +419,6 @@
       <c r="E3">
         <v>31.68724279835391</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -449,9 +438,6 @@
       <c r="E4">
         <v>22.74509803921569</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -471,9 +457,6 @@
       <c r="E5">
         <v>19.6078431372549</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -493,9 +476,6 @@
       <c r="E6">
         <v>28.27004219409282</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -515,9 +495,6 @@
       <c r="E7">
         <v>21.12068965517242</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -537,9 +514,6 @@
       <c r="E8">
         <v>21.39737991266375</v>
       </c>
-      <c r="F8" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -559,9 +533,6 @@
       <c r="E9">
         <v>19.73684210526316</v>
       </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -580,9 +551,6 @@
       </c>
       <c r="E10">
         <v>13.1979695431472</v>
-      </c>
-      <c r="F10" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_peringrmin_a_2024_atacama.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2024_atacama.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -480,76 +480,95 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Huasco</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B7">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="C7">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="D7">
-        <v>0.4900000000000002</v>
+        <v>0.48</v>
       </c>
       <c r="E7">
-        <v>21.12068965517242</v>
+        <v>20.25316455696202</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tierra Amarilla</t>
+          <t>Huasco</t>
         </is>
       </c>
       <c r="B8">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="C8">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="D8">
-        <v>0.4899999999999998</v>
+        <v>0.4900000000000002</v>
       </c>
       <c r="E8">
-        <v>21.39737991266375</v>
+        <v>21.12068965517242</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Tierra Amarilla</t>
         </is>
       </c>
       <c r="B9">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="C9">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="D9">
-        <v>0.4500000000000002</v>
+        <v>0.4899999999999998</v>
       </c>
       <c r="E9">
-        <v>19.73684210526316</v>
+        <v>21.39737991266375</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>2.73</v>
+      </c>
+      <c r="C10">
+        <v>2.28</v>
+      </c>
+      <c r="D10">
+        <v>0.4500000000000002</v>
+      </c>
+      <c r="E10">
+        <v>19.73684210526316</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Diego de Almagro</t>
         </is>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>2.23</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <v>1.97</v>
       </c>
-      <c r="D10">
+      <c r="D11">
         <v>0.26</v>
       </c>
-      <c r="E10">
+      <c r="E11">
         <v>13.1979695431472</v>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_i_peringrmin_a_2024_atacama.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2024_atacama.xlsx
@@ -579,7 +579,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -588,11 +588,6 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -600,28 +595,19 @@
           <t>Alto del Carmen</t>
         </is>
       </c>
-      <c r="B2">
-        <v>5.57</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Caldera</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>3.13</v>
+          <t>Freirina</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Chañaral</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>3.04</v>
+          <t>Huasco</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -630,48 +616,33 @@
           <t>Copiapó</t>
         </is>
       </c>
-      <c r="B5">
-        <v>2.73</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Diego de Almagro</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>2.23</v>
+          <t>Caldera</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Freirina</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>3.2</v>
+          <t>Chañaral</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Huasco</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>2.81</v>
+          <t>Tierra Amarilla</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tierra Amarilla</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>2.78</v>
+          <t>Diego de Almagro</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -679,9 +650,6 @@
         <is>
           <t>Vallenar</t>
         </is>
-      </c>
-      <c r="B10">
-        <v>3.05</v>
       </c>
     </row>
   </sheetData>
